--- a/artfynd/A 31842-2026 artfynd.xlsx
+++ b/artfynd/A 31842-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135568910</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135568921</v>
       </c>
       <c r="B3" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135568925</v>
       </c>
       <c r="B4" t="n">
-        <v>99533</v>
+        <v>99580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135568902</v>
       </c>
       <c r="B5" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135568903</v>
       </c>
       <c r="B6" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135568904</v>
       </c>
       <c r="B7" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>135568905</v>
       </c>
       <c r="B8" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135568906</v>
       </c>
       <c r="B9" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>135568907</v>
       </c>
       <c r="B10" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135568908</v>
       </c>
       <c r="B11" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>135568909</v>
       </c>
       <c r="B12" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>135568911</v>
       </c>
       <c r="B13" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>135568912</v>
       </c>
       <c r="B14" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>135568914</v>
       </c>
       <c r="B15" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>135568915</v>
       </c>
       <c r="B16" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135568916</v>
       </c>
       <c r="B17" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>135568918</v>
       </c>
       <c r="B18" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>135568924</v>
       </c>
       <c r="B19" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135568926</v>
       </c>
       <c r="B20" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>135568927</v>
       </c>
       <c r="B21" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>135568929</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>135568930</v>
       </c>
       <c r="B23" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>135568931</v>
       </c>
       <c r="B24" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>135568932</v>
       </c>
       <c r="B25" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>135568933</v>
       </c>
       <c r="B26" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>135568934</v>
       </c>
       <c r="B27" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135568935</v>
       </c>
       <c r="B28" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>135568937</v>
       </c>
       <c r="B29" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>135568938</v>
       </c>
       <c r="B30" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135568939</v>
       </c>
       <c r="B31" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135568922</v>
       </c>
       <c r="B32" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>135568920</v>
       </c>
       <c r="B33" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135568923</v>
       </c>
       <c r="B34" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>135568959</v>
       </c>
       <c r="B35" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135568958</v>
       </c>
       <c r="B36" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135568960</v>
       </c>
       <c r="B37" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>135568897</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>135568898</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>135568899</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>135568896</v>
       </c>
       <c r="B41" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>135568954</v>
       </c>
       <c r="B42" t="n">
-        <v>99533</v>
+        <v>99580</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>135569007</v>
       </c>
       <c r="B43" t="n">
-        <v>99533</v>
+        <v>99580</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>135569010</v>
       </c>
       <c r="B44" t="n">
-        <v>99533</v>
+        <v>99580</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>135568919</v>
       </c>
       <c r="B45" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>135568917</v>
       </c>
       <c r="B46" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135568940</v>
       </c>
       <c r="B47" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>135568941</v>
       </c>
       <c r="B48" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>135568942</v>
       </c>
       <c r="B49" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>135568943</v>
       </c>
       <c r="B50" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>135568944</v>
       </c>
       <c r="B51" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>135568945</v>
       </c>
       <c r="B52" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>135568946</v>
       </c>
       <c r="B53" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135568947</v>
       </c>
       <c r="B54" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>135568948</v>
       </c>
       <c r="B55" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>135568950</v>
       </c>
       <c r="B56" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>135568951</v>
       </c>
       <c r="B57" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>135568953</v>
       </c>
       <c r="B58" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>135568975</v>
       </c>
       <c r="B59" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>135568976</v>
       </c>
       <c r="B60" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>135568977</v>
       </c>
       <c r="B61" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135568978</v>
       </c>
       <c r="B62" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>135568979</v>
       </c>
       <c r="B63" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>135568980</v>
       </c>
       <c r="B64" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>135568981</v>
       </c>
       <c r="B65" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>135568982</v>
       </c>
       <c r="B66" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>135568983</v>
       </c>
       <c r="B67" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>135568984</v>
       </c>
       <c r="B68" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>135568985</v>
       </c>
       <c r="B69" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>135568986</v>
       </c>
       <c r="B70" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>135568987</v>
       </c>
       <c r="B71" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>135568989</v>
       </c>
       <c r="B72" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>135568990</v>
       </c>
       <c r="B73" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>135568991</v>
       </c>
       <c r="B74" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>135568993</v>
       </c>
       <c r="B75" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>135568994</v>
       </c>
       <c r="B76" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>135568995</v>
       </c>
       <c r="B77" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>135568996</v>
       </c>
       <c r="B78" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>135568997</v>
       </c>
       <c r="B79" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>135568998</v>
       </c>
       <c r="B80" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>135568999</v>
       </c>
       <c r="B81" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>135569000</v>
       </c>
       <c r="B82" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>135569001</v>
       </c>
       <c r="B83" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>135569002</v>
       </c>
       <c r="B84" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>135569003</v>
       </c>
       <c r="B85" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>135569004</v>
       </c>
       <c r="B86" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>135568955</v>
       </c>
       <c r="B87" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>135569006</v>
       </c>
       <c r="B88" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>135569009</v>
       </c>
       <c r="B89" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>135568957</v>
       </c>
       <c r="B90" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 31842-2026 artfynd.xlsx
+++ b/artfynd/A 31842-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135568921</v>
       </c>
       <c r="B3" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135568925</v>
       </c>
       <c r="B4" t="n">
-        <v>99580</v>
+        <v>99607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135568902</v>
       </c>
       <c r="B5" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135568903</v>
       </c>
       <c r="B6" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135568904</v>
       </c>
       <c r="B7" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>135568905</v>
       </c>
       <c r="B8" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135568906</v>
       </c>
       <c r="B9" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>135568907</v>
       </c>
       <c r="B10" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135568908</v>
       </c>
       <c r="B11" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>135568909</v>
       </c>
       <c r="B12" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>135568911</v>
       </c>
       <c r="B13" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>135568912</v>
       </c>
       <c r="B14" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>135568914</v>
       </c>
       <c r="B15" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>135568915</v>
       </c>
       <c r="B16" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135568916</v>
       </c>
       <c r="B17" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>135568918</v>
       </c>
       <c r="B18" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>135568924</v>
       </c>
       <c r="B19" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135568926</v>
       </c>
       <c r="B20" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>135568927</v>
       </c>
       <c r="B21" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>135568929</v>
       </c>
       <c r="B22" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>135568930</v>
       </c>
       <c r="B23" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>135568931</v>
       </c>
       <c r="B24" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>135568932</v>
       </c>
       <c r="B25" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>135568933</v>
       </c>
       <c r="B26" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>135568934</v>
       </c>
       <c r="B27" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135568935</v>
       </c>
       <c r="B28" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>135568937</v>
       </c>
       <c r="B29" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>135568938</v>
       </c>
       <c r="B30" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135568939</v>
       </c>
       <c r="B31" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135568922</v>
       </c>
       <c r="B32" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>135568920</v>
       </c>
       <c r="B33" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135568923</v>
       </c>
       <c r="B34" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>135568959</v>
       </c>
       <c r="B35" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135568958</v>
       </c>
       <c r="B36" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135568960</v>
       </c>
       <c r="B37" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>135568897</v>
       </c>
       <c r="B38" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>135568898</v>
       </c>
       <c r="B39" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>135568899</v>
       </c>
       <c r="B40" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>135568896</v>
       </c>
       <c r="B41" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>135568954</v>
       </c>
       <c r="B42" t="n">
-        <v>99580</v>
+        <v>99607</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>135569007</v>
       </c>
       <c r="B43" t="n">
-        <v>99580</v>
+        <v>99607</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>135569010</v>
       </c>
       <c r="B44" t="n">
-        <v>99580</v>
+        <v>99607</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>135568919</v>
       </c>
       <c r="B45" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>135568917</v>
       </c>
       <c r="B46" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135568940</v>
       </c>
       <c r="B47" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>135568941</v>
       </c>
       <c r="B48" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>135568942</v>
       </c>
       <c r="B49" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>135568943</v>
       </c>
       <c r="B50" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>135568944</v>
       </c>
       <c r="B51" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>135568945</v>
       </c>
       <c r="B52" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>135568946</v>
       </c>
       <c r="B53" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135568947</v>
       </c>
       <c r="B54" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>135568948</v>
       </c>
       <c r="B55" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>135568950</v>
       </c>
       <c r="B56" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>135568951</v>
       </c>
       <c r="B57" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>135568953</v>
       </c>
       <c r="B58" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>135568975</v>
       </c>
       <c r="B59" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>135568976</v>
       </c>
       <c r="B60" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>135568977</v>
       </c>
       <c r="B61" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135568978</v>
       </c>
       <c r="B62" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>135568979</v>
       </c>
       <c r="B63" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>135568980</v>
       </c>
       <c r="B64" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>135568981</v>
       </c>
       <c r="B65" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>135568982</v>
       </c>
       <c r="B66" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>135568983</v>
       </c>
       <c r="B67" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>135568984</v>
       </c>
       <c r="B68" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>135568985</v>
       </c>
       <c r="B69" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>135568986</v>
       </c>
       <c r="B70" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>135568987</v>
       </c>
       <c r="B71" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>135568989</v>
       </c>
       <c r="B72" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>135568990</v>
       </c>
       <c r="B73" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>135568991</v>
       </c>
       <c r="B74" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>135568993</v>
       </c>
       <c r="B75" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>135568994</v>
       </c>
       <c r="B76" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>135568995</v>
       </c>
       <c r="B77" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>135568996</v>
       </c>
       <c r="B78" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>135568997</v>
       </c>
       <c r="B79" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>135568998</v>
       </c>
       <c r="B80" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>135568999</v>
       </c>
       <c r="B81" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>135569000</v>
       </c>
       <c r="B82" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>135569001</v>
       </c>
       <c r="B83" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>135569002</v>
       </c>
       <c r="B84" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>135569003</v>
       </c>
       <c r="B85" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>135569004</v>
       </c>
       <c r="B86" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>135568955</v>
       </c>
       <c r="B87" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>135569006</v>
       </c>
       <c r="B88" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>135569009</v>
       </c>
       <c r="B89" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>135568957</v>
       </c>
       <c r="B90" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 31842-2026 artfynd.xlsx
+++ b/artfynd/A 31842-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135568921</v>
       </c>
       <c r="B3" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135568925</v>
       </c>
       <c r="B4" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135568902</v>
       </c>
       <c r="B5" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135568903</v>
       </c>
       <c r="B6" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135568904</v>
       </c>
       <c r="B7" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>135568905</v>
       </c>
       <c r="B8" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135568906</v>
       </c>
       <c r="B9" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>135568907</v>
       </c>
       <c r="B10" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135568908</v>
       </c>
       <c r="B11" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>135568909</v>
       </c>
       <c r="B12" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>135568911</v>
       </c>
       <c r="B13" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>135568912</v>
       </c>
       <c r="B14" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>135568914</v>
       </c>
       <c r="B15" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>135568915</v>
       </c>
       <c r="B16" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135568916</v>
       </c>
       <c r="B17" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>135568918</v>
       </c>
       <c r="B18" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>135568924</v>
       </c>
       <c r="B19" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135568926</v>
       </c>
       <c r="B20" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>135568927</v>
       </c>
       <c r="B21" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>135568929</v>
       </c>
       <c r="B22" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>135568930</v>
       </c>
       <c r="B23" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>135568931</v>
       </c>
       <c r="B24" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>135568932</v>
       </c>
       <c r="B25" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>135568933</v>
       </c>
       <c r="B26" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>135568934</v>
       </c>
       <c r="B27" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135568935</v>
       </c>
       <c r="B28" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>135568937</v>
       </c>
       <c r="B29" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>135568938</v>
       </c>
       <c r="B30" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135568939</v>
       </c>
       <c r="B31" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135568922</v>
       </c>
       <c r="B32" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>135568920</v>
       </c>
       <c r="B33" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135568923</v>
       </c>
       <c r="B34" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>135568959</v>
       </c>
       <c r="B35" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135568958</v>
       </c>
       <c r="B36" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135568960</v>
       </c>
       <c r="B37" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>135568954</v>
       </c>
       <c r="B42" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>135569007</v>
       </c>
       <c r="B43" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>135569010</v>
       </c>
       <c r="B44" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>135568919</v>
       </c>
       <c r="B45" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>135568917</v>
       </c>
       <c r="B46" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135568940</v>
       </c>
       <c r="B47" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>135568941</v>
       </c>
       <c r="B48" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>135568942</v>
       </c>
       <c r="B49" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>135568943</v>
       </c>
       <c r="B50" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>135568944</v>
       </c>
       <c r="B51" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>135568945</v>
       </c>
       <c r="B52" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>135568946</v>
       </c>
       <c r="B53" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135568947</v>
       </c>
       <c r="B54" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>135568948</v>
       </c>
       <c r="B55" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>135568950</v>
       </c>
       <c r="B56" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>135568951</v>
       </c>
       <c r="B57" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>135568953</v>
       </c>
       <c r="B58" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>135568975</v>
       </c>
       <c r="B59" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>135568976</v>
       </c>
       <c r="B60" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>135568977</v>
       </c>
       <c r="B61" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135568978</v>
       </c>
       <c r="B62" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>135568979</v>
       </c>
       <c r="B63" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>135568980</v>
       </c>
       <c r="B64" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>135568981</v>
       </c>
       <c r="B65" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>135568982</v>
       </c>
       <c r="B66" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>135568983</v>
       </c>
       <c r="B67" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>135568984</v>
       </c>
       <c r="B68" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>135568985</v>
       </c>
       <c r="B69" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>135568986</v>
       </c>
       <c r="B70" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>135568987</v>
       </c>
       <c r="B71" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>135568989</v>
       </c>
       <c r="B72" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>135568990</v>
       </c>
       <c r="B73" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>135568991</v>
       </c>
       <c r="B74" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>135568993</v>
       </c>
       <c r="B75" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>135568994</v>
       </c>
       <c r="B76" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>135568995</v>
       </c>
       <c r="B77" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>135568996</v>
       </c>
       <c r="B78" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>135568997</v>
       </c>
       <c r="B79" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>135568998</v>
       </c>
       <c r="B80" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>135568999</v>
       </c>
       <c r="B81" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>135569000</v>
       </c>
       <c r="B82" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>135569001</v>
       </c>
       <c r="B83" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>135569002</v>
       </c>
       <c r="B84" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>135569003</v>
       </c>
       <c r="B85" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>135569004</v>
       </c>
       <c r="B86" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>135568955</v>
       </c>
       <c r="B87" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>135569006</v>
       </c>
       <c r="B88" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>135569009</v>
       </c>
       <c r="B89" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>135568957</v>
       </c>
       <c r="B90" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 31842-2026 artfynd.xlsx
+++ b/artfynd/A 31842-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135568910</v>
       </c>
       <c r="B2" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135568921</v>
       </c>
       <c r="B3" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135568925</v>
       </c>
       <c r="B4" t="n">
-        <v>99614</v>
+        <v>99631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135568902</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135568903</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135568904</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>135568905</v>
       </c>
       <c r="B8" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135568906</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>135568907</v>
       </c>
       <c r="B10" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135568908</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>135568909</v>
       </c>
       <c r="B12" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>135568911</v>
       </c>
       <c r="B13" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>135568912</v>
       </c>
       <c r="B14" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>135568914</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>135568915</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135568916</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>135568918</v>
       </c>
       <c r="B18" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>135568924</v>
       </c>
       <c r="B19" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135568926</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>135568927</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>135568929</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>135568930</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>135568931</v>
       </c>
       <c r="B24" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>135568932</v>
       </c>
       <c r="B25" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>135568933</v>
       </c>
       <c r="B26" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>135568934</v>
       </c>
       <c r="B27" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135568935</v>
       </c>
       <c r="B28" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>135568937</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>135568938</v>
       </c>
       <c r="B30" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135568939</v>
       </c>
       <c r="B31" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135568922</v>
       </c>
       <c r="B32" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>135568920</v>
       </c>
       <c r="B33" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135568923</v>
       </c>
       <c r="B34" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>135568959</v>
       </c>
       <c r="B35" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135568958</v>
       </c>
       <c r="B36" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135568960</v>
       </c>
       <c r="B37" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>135568897</v>
       </c>
       <c r="B38" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>135568898</v>
       </c>
       <c r="B39" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>135568899</v>
       </c>
       <c r="B40" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>135568896</v>
       </c>
       <c r="B41" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>135568954</v>
       </c>
       <c r="B42" t="n">
-        <v>99614</v>
+        <v>99631</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>135569007</v>
       </c>
       <c r="B43" t="n">
-        <v>99614</v>
+        <v>99631</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>135569010</v>
       </c>
       <c r="B44" t="n">
-        <v>99614</v>
+        <v>99631</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>135568919</v>
       </c>
       <c r="B45" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>135568917</v>
       </c>
       <c r="B46" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135568940</v>
       </c>
       <c r="B47" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>135568941</v>
       </c>
       <c r="B48" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>135568942</v>
       </c>
       <c r="B49" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>135568943</v>
       </c>
       <c r="B50" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>135568944</v>
       </c>
       <c r="B51" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>135568945</v>
       </c>
       <c r="B52" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>135568946</v>
       </c>
       <c r="B53" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135568947</v>
       </c>
       <c r="B54" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>135568948</v>
       </c>
       <c r="B55" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>135568950</v>
       </c>
       <c r="B56" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>135568951</v>
       </c>
       <c r="B57" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>135568953</v>
       </c>
       <c r="B58" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>135568975</v>
       </c>
       <c r="B59" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>135568976</v>
       </c>
       <c r="B60" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>135568977</v>
       </c>
       <c r="B61" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135568978</v>
       </c>
       <c r="B62" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>135568979</v>
       </c>
       <c r="B63" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>135568980</v>
       </c>
       <c r="B64" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>135568981</v>
       </c>
       <c r="B65" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>135568982</v>
       </c>
       <c r="B66" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>135568983</v>
       </c>
       <c r="B67" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>135568984</v>
       </c>
       <c r="B68" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>135568985</v>
       </c>
       <c r="B69" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>135568986</v>
       </c>
       <c r="B70" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>135568987</v>
       </c>
       <c r="B71" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>135568989</v>
       </c>
       <c r="B72" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>135568990</v>
       </c>
       <c r="B73" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>135568991</v>
       </c>
       <c r="B74" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>135568993</v>
       </c>
       <c r="B75" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>135568994</v>
       </c>
       <c r="B76" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>135568995</v>
       </c>
       <c r="B77" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>135568996</v>
       </c>
       <c r="B78" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>135568997</v>
       </c>
       <c r="B79" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>135568998</v>
       </c>
       <c r="B80" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>135568999</v>
       </c>
       <c r="B81" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>135569000</v>
       </c>
       <c r="B82" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>135569001</v>
       </c>
       <c r="B83" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>135569002</v>
       </c>
       <c r="B84" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>135569003</v>
       </c>
       <c r="B85" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>135569004</v>
       </c>
       <c r="B86" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>135568955</v>
       </c>
       <c r="B87" t="n">
-        <v>110014</v>
+        <v>110037</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>135569006</v>
       </c>
       <c r="B88" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>135569009</v>
       </c>
       <c r="B89" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>135568957</v>
       </c>
       <c r="B90" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 31842-2026 artfynd.xlsx
+++ b/artfynd/A 31842-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135568921</v>
       </c>
       <c r="B3" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135568925</v>
       </c>
       <c r="B4" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135568902</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135568903</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135568904</v>
       </c>
       <c r="B7" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>135568905</v>
       </c>
       <c r="B8" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135568906</v>
       </c>
       <c r="B9" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>135568907</v>
       </c>
       <c r="B10" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135568908</v>
       </c>
       <c r="B11" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>135568909</v>
       </c>
       <c r="B12" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>135568911</v>
       </c>
       <c r="B13" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>135568912</v>
       </c>
       <c r="B14" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>135568914</v>
       </c>
       <c r="B15" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>135568915</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135568916</v>
       </c>
       <c r="B17" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>135568918</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>135568924</v>
       </c>
       <c r="B19" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135568926</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>135568927</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>135568929</v>
       </c>
       <c r="B22" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>135568930</v>
       </c>
       <c r="B23" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>135568931</v>
       </c>
       <c r="B24" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>135568932</v>
       </c>
       <c r="B25" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>135568933</v>
       </c>
       <c r="B26" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>135568934</v>
       </c>
       <c r="B27" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135568935</v>
       </c>
       <c r="B28" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>135568937</v>
       </c>
       <c r="B29" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>135568938</v>
       </c>
       <c r="B30" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135568939</v>
       </c>
       <c r="B31" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135568922</v>
       </c>
       <c r="B32" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>135568920</v>
       </c>
       <c r="B33" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135568923</v>
       </c>
       <c r="B34" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>135568959</v>
       </c>
       <c r="B35" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135568958</v>
       </c>
       <c r="B36" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135568960</v>
       </c>
       <c r="B37" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>135568897</v>
       </c>
       <c r="B38" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>135568898</v>
       </c>
       <c r="B39" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>135568899</v>
       </c>
       <c r="B40" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>135568896</v>
       </c>
       <c r="B41" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>135568954</v>
       </c>
       <c r="B42" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>135569007</v>
       </c>
       <c r="B43" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>135569010</v>
       </c>
       <c r="B44" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>135568919</v>
       </c>
       <c r="B45" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>135568917</v>
       </c>
       <c r="B46" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135568940</v>
       </c>
       <c r="B47" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>135568941</v>
       </c>
       <c r="B48" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>135568942</v>
       </c>
       <c r="B49" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>135568943</v>
       </c>
       <c r="B50" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>135568944</v>
       </c>
       <c r="B51" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>135568945</v>
       </c>
       <c r="B52" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>135568946</v>
       </c>
       <c r="B53" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135568947</v>
       </c>
       <c r="B54" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>135568948</v>
       </c>
       <c r="B55" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>135568950</v>
       </c>
       <c r="B56" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>135568951</v>
       </c>
       <c r="B57" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>135568953</v>
       </c>
       <c r="B58" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>135568975</v>
       </c>
       <c r="B59" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>135568976</v>
       </c>
       <c r="B60" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>135568977</v>
       </c>
       <c r="B61" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135568978</v>
       </c>
       <c r="B62" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>135568979</v>
       </c>
       <c r="B63" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>135568980</v>
       </c>
       <c r="B64" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>135568981</v>
       </c>
       <c r="B65" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>135568982</v>
       </c>
       <c r="B66" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>135568983</v>
       </c>
       <c r="B67" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>135568984</v>
       </c>
       <c r="B68" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>135568985</v>
       </c>
       <c r="B69" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>135568986</v>
       </c>
       <c r="B70" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>135568987</v>
       </c>
       <c r="B71" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>135568989</v>
       </c>
       <c r="B72" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>135568990</v>
       </c>
       <c r="B73" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>135568991</v>
       </c>
       <c r="B74" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>135568993</v>
       </c>
       <c r="B75" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>135568994</v>
       </c>
       <c r="B76" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>135568995</v>
       </c>
       <c r="B77" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>135568996</v>
       </c>
       <c r="B78" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>135568997</v>
       </c>
       <c r="B79" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>135568998</v>
       </c>
       <c r="B80" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>135568999</v>
       </c>
       <c r="B81" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>135569000</v>
       </c>
       <c r="B82" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>135569001</v>
       </c>
       <c r="B83" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>135569002</v>
       </c>
       <c r="B84" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>135569003</v>
       </c>
       <c r="B85" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>135569004</v>
       </c>
       <c r="B86" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>135568955</v>
       </c>
       <c r="B87" t="n">
-        <v>110037</v>
+        <v>110039</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>135569006</v>
       </c>
       <c r="B88" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>135569009</v>
       </c>
       <c r="B89" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>135568957</v>
       </c>
       <c r="B90" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 31842-2026 artfynd.xlsx
+++ b/artfynd/A 31842-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135568921</v>
       </c>
       <c r="B3" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135568925</v>
       </c>
       <c r="B4" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135568902</v>
       </c>
       <c r="B5" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135568903</v>
       </c>
       <c r="B6" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135568904</v>
       </c>
       <c r="B7" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>135568905</v>
       </c>
       <c r="B8" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135568906</v>
       </c>
       <c r="B9" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>135568907</v>
       </c>
       <c r="B10" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135568908</v>
       </c>
       <c r="B11" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>135568909</v>
       </c>
       <c r="B12" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>135568911</v>
       </c>
       <c r="B13" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>135568912</v>
       </c>
       <c r="B14" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>135568914</v>
       </c>
       <c r="B15" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>135568915</v>
       </c>
       <c r="B16" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135568916</v>
       </c>
       <c r="B17" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>135568918</v>
       </c>
       <c r="B18" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>135568924</v>
       </c>
       <c r="B19" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135568926</v>
       </c>
       <c r="B20" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>135568927</v>
       </c>
       <c r="B21" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>135568929</v>
       </c>
       <c r="B22" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>135568930</v>
       </c>
       <c r="B23" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>135568931</v>
       </c>
       <c r="B24" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>135568932</v>
       </c>
       <c r="B25" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>135568933</v>
       </c>
       <c r="B26" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>135568934</v>
       </c>
       <c r="B27" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135568935</v>
       </c>
       <c r="B28" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>135568937</v>
       </c>
       <c r="B29" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>135568938</v>
       </c>
       <c r="B30" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>135568939</v>
       </c>
       <c r="B31" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135568922</v>
       </c>
       <c r="B32" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>135568920</v>
       </c>
       <c r="B33" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135568923</v>
       </c>
       <c r="B34" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>135568959</v>
       </c>
       <c r="B35" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135568958</v>
       </c>
       <c r="B36" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135568960</v>
       </c>
       <c r="B37" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>135568954</v>
       </c>
       <c r="B42" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>135569007</v>
       </c>
       <c r="B43" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>135569010</v>
       </c>
       <c r="B44" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>135568919</v>
       </c>
       <c r="B45" t="n">
-        <v>108319</v>
+        <v>108320</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>135568917</v>
       </c>
       <c r="B46" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135568940</v>
       </c>
       <c r="B47" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>135568941</v>
       </c>
       <c r="B48" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>135568942</v>
       </c>
       <c r="B49" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>135568943</v>
       </c>
       <c r="B50" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>135568944</v>
       </c>
       <c r="B51" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>135568945</v>
       </c>
       <c r="B52" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>135568946</v>
       </c>
       <c r="B53" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135568947</v>
       </c>
       <c r="B54" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>135568948</v>
       </c>
       <c r="B55" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>135568950</v>
       </c>
       <c r="B56" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>135568951</v>
       </c>
       <c r="B57" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>135568953</v>
       </c>
       <c r="B58" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>135568975</v>
       </c>
       <c r="B59" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>135568976</v>
       </c>
       <c r="B60" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>135568977</v>
       </c>
       <c r="B61" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135568978</v>
       </c>
       <c r="B62" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>135568979</v>
       </c>
       <c r="B63" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>135568980</v>
       </c>
       <c r="B64" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>135568981</v>
       </c>
       <c r="B65" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>135568982</v>
       </c>
       <c r="B66" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>135568983</v>
       </c>
       <c r="B67" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>135568984</v>
       </c>
       <c r="B68" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>135568985</v>
       </c>
       <c r="B69" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>135568986</v>
       </c>
       <c r="B70" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>135568987</v>
       </c>
       <c r="B71" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>135568989</v>
       </c>
       <c r="B72" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>135568990</v>
       </c>
       <c r="B73" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>135568991</v>
       </c>
       <c r="B74" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>135568993</v>
       </c>
       <c r="B75" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>135568994</v>
       </c>
       <c r="B76" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>135568995</v>
       </c>
       <c r="B77" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>135568996</v>
       </c>
       <c r="B78" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>135568997</v>
       </c>
       <c r="B79" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>135568998</v>
       </c>
       <c r="B80" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>135568999</v>
       </c>
       <c r="B81" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>135569000</v>
       </c>
       <c r="B82" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>135569001</v>
       </c>
       <c r="B83" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>135569002</v>
       </c>
       <c r="B84" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>135569003</v>
       </c>
       <c r="B85" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>135569004</v>
       </c>
       <c r="B86" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>135568955</v>
       </c>
       <c r="B87" t="n">
-        <v>110039</v>
+        <v>110040</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>135569006</v>
       </c>
       <c r="B88" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>135569009</v>
       </c>
       <c r="B89" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>135568957</v>
       </c>
       <c r="B90" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
